--- a/data/trans_orig/P05B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05B_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>53148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86953</t>
+          <t>83826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81346</t>
+          <t>82420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118863</t>
+          <t>122392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985940</t>
+          <t>985262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1007725</t>
+          <t>1007309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1228160</t>
+          <t>1231287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1261236</t>
+          <t>1261965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2226206</t>
+          <t>2222677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2263723</t>
+          <t>2262649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64058</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87993</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97230</t>
+          <t>96933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138257</t>
+          <t>143106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1629355</t>
+          <t>1628453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1657220</t>
+          <t>1658435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1498056</t>
+          <t>1498513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1530117</t>
+          <t>1530662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3141205</t>
+          <t>3136356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3182232</t>
+          <t>3182529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>51202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522140</t>
+          <t>522591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539189</t>
+          <t>539564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443232</t>
+          <t>445052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462979</t>
+          <t>463149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>973829</t>
+          <t>974264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999512</t>
+          <t>999873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118038</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183332</t>
+          <t>183299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224001</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>289010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3154386</t>
+          <t>3153265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3194603</t>
+          <t>3193198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3194241</t>
+          <t>3194274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3241790</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6360906</t>
+          <t>6360987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6425996</t>
+          <t>6424960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947680</t>
+          <t>948140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>962800</t>
+          <t>962921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1298205</t>
+          <t>1299722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1317351</t>
+          <t>1316746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2253324</t>
+          <t>2252719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2275729</t>
+          <t>2276797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,82 +2694,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>35484</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25124</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49155</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>67175</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>51399</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>86347</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35484</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24646</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>49541</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>67175</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>50826</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>86817</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1911589</t>
+          <t>1912576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936578</t>
+          <t>1935970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,82 +2807,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1717194</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1703523</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1727554</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3418</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3642640</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3623468</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3658416</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>97,67%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1597</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1717194</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1703137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1728032</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3642640</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3622998</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3658989</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458103</t>
+          <t>457447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472823</t>
+          <t>472511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447607</t>
+          <t>446931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455857</t>
+          <t>455843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>910375</t>
+          <t>909803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926609</t>
+          <t>926716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42844</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75039</t>
+          <t>74446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75022</t>
+          <t>74893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94252</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137763</t>
+          <t>136359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3330766</t>
+          <t>3331359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3362961</t>
+          <t>3364195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3462487</t>
+          <t>3462616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3495327</t>
+          <t>3492731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6805551</t>
+          <t>6806955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6849062</t>
+          <t>6850805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37969</t>
+          <t>38063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735963</t>
+          <t>735500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747914</t>
+          <t>747506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>949516</t>
+          <t>949422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>971111</t>
+          <t>970783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1690339</t>
+          <t>1690891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1715402</t>
+          <t>1715180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20325</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43151</t>
+          <t>42019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55243</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>89478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026896</t>
+          <t>2028028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2049722</t>
+          <t>2050082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1925235</t>
+          <t>1926969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1951658</t>
+          <t>1951829</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3961206</t>
+          <t>3962015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3996250</t>
+          <t>3997278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528590</t>
+          <t>529623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543244</t>
+          <t>543192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533551</t>
+          <t>532585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544960</t>
+          <t>544943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1069383</t>
+          <t>1068835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1086926</t>
+          <t>1086311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60126</t>
+          <t>61192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60196</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94702</t>
+          <t>96336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102616</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147386</t>
+          <t>145953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3308776</t>
+          <t>3307710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3336397</t>
+          <t>3335177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3423369</t>
+          <t>3421735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3457875</t>
+          <t>3457657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6739587</t>
+          <t>6741020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6784357</t>
+          <t>6785941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500195</t>
+          <t>562490</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492635</t>
+          <t>554659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505592</t>
+          <t>567516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>739141</t>
+          <t>805119</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>731833</t>
+          <t>798164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>743748</t>
+          <t>809941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1239336</t>
+          <t>1367609</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1229295</t>
+          <t>1357960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1247009</t>
+          <t>1375086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,47 +5900,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>22094</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15059</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32306</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20975</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13435</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30936</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34387</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>48413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2275678</t>
+          <t>2216116</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2265661</t>
+          <t>2205226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2283058</t>
+          <t>2222202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,47 +6013,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2146281</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2136069</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2153316</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2214437</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2204476</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4490115</t>
+          <t>4362398</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4475608</t>
+          <t>4349224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4500442</t>
+          <t>4371716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,47 +6243,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20403</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11451</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18923</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>633547</t>
+          <t>697341</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623794</t>
+          <t>686237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639125</t>
+          <t>703423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,49 +6356,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>720056</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>711864</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>725347</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>646598</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>639126</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>651889</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1651</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1280145</t>
+          <t>1417397</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268833</t>
+          <t>1404817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287810</t>
+          <t>1425499</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33494</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59525</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65943</t>
+          <t>69374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>107159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6679,17 +6679,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3409421</t>
+          <t>3475948</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3393177</t>
+          <t>3460213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3421873</t>
+          <t>3486207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3600175</t>
+          <t>3671454</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3586063</t>
+          <t>3656108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3612094</t>
+          <t>3681828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7009596</t>
+          <t>7147402</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6988192</t>
+          <t>7125716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7026231</t>
+          <t>7163501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
